--- a/.files/TEST_Report.xlsx
+++ b/.files/TEST_Report.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Elev 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Elev 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Elev 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -335,6 +337,66 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2667000" cy="2000250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>6</col>
       <colOff>0</colOff>
       <row>39</row>
@@ -650,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -660,10 +722,10 @@
     <col width="99" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="2" customWidth="1" min="10" max="10"/>
-    <col width="2" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,7 +790,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Elev 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -743,14 +805,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
+          <t>8ft, 8ft, 8ft, 8ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>838</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>514.532</v>
+        <v>1257</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 8ft, 8ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft, 3ft</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1257</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>719.0039999999999</v>
       </c>
     </row>
     <row r="4">
@@ -760,7 +835,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -774,14 +849,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8ft x 3</t>
+          <t>8ft x 6</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>300</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>171.6</v>
       </c>
     </row>
     <row r="5">
@@ -805,14 +893,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8ft x 3</t>
+          <t>8ft x 6</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>497</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>305.158</v>
+        <v>994</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>994</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>568.568</v>
       </c>
     </row>
     <row r="6">
@@ -836,14 +937,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3ft x 4</t>
+          <t>3ft x 8</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
         <v>527</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>323.578</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>301.444</v>
       </c>
     </row>
     <row r="7">
@@ -869,14 +983,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3ft x 4</t>
+          <t>3ft x 8</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
         <v>444</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>272.616</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>253.968</v>
       </c>
     </row>
     <row r="8">
@@ -902,14 +1029,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12ft</t>
+          <t>12ft x 2</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
         <v>264</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>162.096</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>12ft x 2</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>151.008</v>
       </c>
     </row>
     <row r="9">
@@ -935,14 +1075,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3ft x 8</t>
+          <t>3ft x 16</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>85.05</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>52.2207</v>
+        <v>170.1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3ft x 16</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>97.29719999999999</v>
       </c>
     </row>
     <row r="10">
@@ -964,10 +1117,10 @@
         </is>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2805.05</v>
+        <v>3956.1</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>1722.3007</v>
+        <v>2262.8892</v>
       </c>
     </row>
     <row r="11">
@@ -995,7 +1148,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>96.00 sqft</t>
+          <t>192.00 sqft</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1047,14 +1200,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.00 pcs</t>
+          <t>4.00 pcs</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
         <v>64.8</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>39.7872</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>37.0656</v>
       </c>
     </row>
     <row r="14">
@@ -1065,7 +1231,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>40.00 ft</t>
+          <t>80.00 ft</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1080,14 +1246,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>73.066</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16.00 pcs</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>68.068</v>
       </c>
     </row>
     <row r="15">
@@ -1098,7 +1277,8 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 x Narrow Door ($1,638.00)
+  with: Concealed Closer, Continuous Hinges</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1113,14 +1293,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56.00 pcs</t>
+          <t>112.00 pcs</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>11.2362</v>
+        <v>36.6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>112.00 pcs</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20.9352</v>
       </c>
     </row>
     <row r="16">
@@ -1146,14 +1339,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.00 pcs</t>
+          <t>24.00 pcs</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
         <v>46.65</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>28.6431</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24.00 pcs</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>26.6838</v>
       </c>
     </row>
     <row r="17">
@@ -1169,14 +1375,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
         <v>48.6</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>29.8404</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>27.7992</v>
       </c>
     </row>
     <row r="18">
@@ -1192,14 +1411,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>22.104</v>
+        <v>72</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16.00 pcs</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>41.184</v>
       </c>
     </row>
     <row r="19">
@@ -1215,14 +1447,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>12.00 pcs</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
         <v>76.95</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>47.2473</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>44.0154</v>
       </c>
     </row>
     <row r="20">
@@ -1238,14 +1483,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
         <v>76.95</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>47.2473</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>16.00 pcs</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>44.0154</v>
       </c>
     </row>
     <row r="21">
@@ -1261,14 +1519,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>90.258</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>84.08399999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1284,14 +1555,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>12.00 pcs</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
         <v>56.7</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>34.8138</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>32.4324</v>
       </c>
     </row>
     <row r="23">
@@ -1307,14 +1591,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>16.00 pcs</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
         <v>95.25</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>58.4835</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>16.00 pcs</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>54.483</v>
       </c>
     </row>
     <row r="24">
@@ -1326,10 +1623,10 @@
         </is>
       </c>
       <c r="H24" s="9" t="n">
-        <v>786.2</v>
+        <v>840.5000000000001</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>482.7268</v>
+        <v>480.766</v>
       </c>
     </row>
     <row r="25">
@@ -1379,14 +1676,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>224.00 ft</t>
+          <t>448.00 ft</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
         <v>405</v>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>248.67</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>448.00 ft</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>231.66</v>
       </c>
     </row>
     <row r="28">
@@ -1401,13 +1711,13 @@
         <v>405</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>248.67</v>
+        <v>231.66</v>
       </c>
     </row>
     <row r="29">
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>GLASS</t>
+          <t>DOORS</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1751,7 @@
     <row r="31">
       <c r="E31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (3' X 7')</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1451,14 +1761,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>83.75 sqft</t>
+          <t>2.00 pcs</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>879.375</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>879.375</v>
+        <v>3276</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>3276</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>3276</v>
       </c>
     </row>
     <row r="32">
@@ -1466,20 +1789,20 @@
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>Total Glass Cost</t>
+          <t>Total Door Cost</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
-        <v>879.375</v>
+        <v>3276</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>879.375</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="33">
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>FABRICATION</t>
+          <t>GLASS</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1836,7 @@
     <row r="35">
       <c r="E35" t="inlineStr">
         <is>
-          <t>Joints Fabrication Labor</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1523,14 +1846,27 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24.00 joints</t>
+          <t>155.95 sqft</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>360</v>
+        <v>1637.475</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>155.95 sqft</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1637.475</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>1637.475</v>
       </c>
     </row>
     <row r="36">
@@ -1538,93 +1874,273 @@
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
+          <t>Total Glass Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>1637.475</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>1637.475</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Door Area (to subtract from glass)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>42.00 sqft</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>42.00 sqft</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Total Calculations Cost</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>FABRICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>48.00 joints</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>48.00 joints</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>720</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
           <t>Total Fabrication Cost</t>
         </is>
       </c>
-      <c r="H36" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="G38" s="4" t="inlineStr">
+      <c r="H44" s="9" t="n">
+        <v>720</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>COST/ELEVATION</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>TOTAL ELEVATION COST</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="G39" t="inlineStr">
+    <row r="47">
+      <c r="G47" t="inlineStr">
         <is>
           <t>PROFILE COSTS</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>1722.3007</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="G40" t="inlineStr">
+      <c r="I47" s="5" t="n">
+        <v>2262.8892</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="inlineStr">
         <is>
           <t>ACCESSORY COSTS</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n">
-        <v>482.7268</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="G41" t="inlineStr">
+      <c r="I48" s="5" t="n">
+        <v>480.766</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" t="inlineStr">
         <is>
           <t>GASKET COSTS</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>248.67</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="G42" t="inlineStr">
+      <c r="I49" s="5" t="n">
+        <v>231.66</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DOOR COSTS</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" t="inlineStr">
         <is>
           <t>GLASS COSTS</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>879.375</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="G43" t="inlineStr">
+      <c r="I51" s="5" t="n">
+        <v>1637.475</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" t="inlineStr">
         <is>
           <t>FABRICATION COSTS</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t>1 TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="G45" s="13" t="inlineStr">
+      <c r="I52" s="5" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Elev 1 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>8608.790199999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" s="13" t="inlineStr">
         <is>
           <t>*Note - Elevation costs based on discounted material costs</t>
         </is>
@@ -1642,15 +2158,2726 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="99" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>System Input</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>YES 45TU FRONT SET(OG)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>PROFILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elevation Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Elev 2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vertical Sill/Jamb Screw Spline Assembly (Jamb) / Horizontal Sill/Jamb Screw Spline Assembly (Sill)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 3ft, 3ft, 3ft, 3ft</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>838</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>479.336</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Total Count</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vertical Flush Filler</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>85.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Bays Wide</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vertical Two Piece Mullion Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>497</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8ft x 3</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>497</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>284.284</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Bays Tall</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Horizontal Horizontal Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>301.444</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Widths</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Horizontal Head</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3ft x 4</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>444</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>253.968</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Heights</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Equal distribution</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thermal Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12ft</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>12ft</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>151.008</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Opening Width</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>144.00 in</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Horizontal Glass Stop (Use with BE9-2514, BE9-2515, BE9-2517)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3ft x 8</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>85.05</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>48.64859999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Opening Height</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>96.00 in</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Total Profile Cost</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2805.05</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>1604.4886</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sq Ft per Type</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total Sq Ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>End Dam For Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2.00 pcs</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>37.0656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Water Deflector</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>68.068</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#12 x 1-1/4” PHSMS Type AB, Zinc Plated Steel, For Screw Spline Attachment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56.00 pcs</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>56.00 pcs</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>10.4676</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Bay Distribution Diagram</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>*Note - C/L Dimensions</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>26.6838</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>27.7992</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Setting Block Chair Use with E2-0177 Setting Block at Sill</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>20.592</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Side Block For Intermediate Vertical Shallow Pocket</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>44.0154</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Setting Block For Sill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>44.0154</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1-1/8” “W” Side Block For Jamb</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4.00 pcs</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>84.08399999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1/2” “W” Side Block For Intermediate Vertical Deep Pocket</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>32.4324</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Setting Block For Intermediate Horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>8.00 pcs</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>54.483</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Total Accessory Cost</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>786.2</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>449.7064</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>GASKETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Glazing Gasket For 1” Glazing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>224.00 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>224.00 ft</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>405</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>231.66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Total Gasket Cost</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>405</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>231.66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>83.75 sqft</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>879.375</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>83.75 sqft</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>879.375</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Total Glass Cost</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>879.375</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>FABRICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>24.00 joints</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>24.00 joints</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Total Fabrication Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>1604.4886</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>449.7064</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>231.66</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>879.375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Elev 2 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>3525.23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>*Note - Elevation costs based on discounted material costs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="99" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="216" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="216" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>System Input</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>YES 45TU FRONT SET(OG)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>PROFILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Elevation Type</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Elev 3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vertical Sill/Jamb Screw Spline Assembly (Jamb) / Horizontal Sill/Jamb Screw Spline Assembly (Sill)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 8ft, 8ft, 8ft, 8ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1676</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BE9-2513</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8ft, 8ft, 8ft, 8ft, 8ft, 8ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1676</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>958.6719999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Total Count</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Vertical Flush Filler</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>E9-2512</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>171.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Bays Wide</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vertical Two Piece Mullion Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>994</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BE9-2511</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8ft x 6</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>994</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>568.568</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Bays Tall</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Horizontal Horizontal Screw Spline Assembly</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1054</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BE9-2515</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1054</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>602.8879999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Widths</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>10.00 in, 67.00 in, 67.00 in</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Horizontal Head</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>888</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BE9-2514</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>888</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>507.936</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Custom Bay Heights</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>38.00 in, 20.00 in, 38.00 in</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thermal Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>12ft x 3</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BE9-2578</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>12ft x 3</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>302.016</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Opening Width</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>144.00 in</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Horizontal Glass Stop (Use with BE9-2514, BE9-2515, BE9-2517)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>425.2499999999999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>E9-2519</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft, 0.83ft, 5.58ft, 5.58ft</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>425.2499999999999</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>243.2429999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Opening Height</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>96.00 in</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Total Profile Cost</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>5865.25</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>3354.923</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Sq Ft per Type</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>96.00 sqft</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ACCESSORIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total Sq Ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>288.00 sqft</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>40.00 ft</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>End Dam For Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E1-0199</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>37.0656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Total Perimeter Ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>120.00 ft</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Water Deflector</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>E2-0047</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>68.068</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>6 x Wide Door ($1,813.25)
+  with: Extended Ladder Pull (Single), Latch Lock w/ Lever Handle</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>#12 x 1-1/4” PHSMS Type AB, Zinc Plated Steel, For Screw Spline Attachment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>180.00 pcs</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PC-1220</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>180.00 pcs</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20.9352</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Bay Distribution Diagram</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>*Note - C/L Dimensions</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>#10-24 x 3/8” PHMS, Stainless Steel, For Attachment of Sill to Sill Flashing</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>27.00 pcs</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PM-1006-SS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>27.00 pcs</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>26.6838</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>#12 x 3/4” UFHSMS Type A, Zinc Plated Steel For End Dam Attachment</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UA-1212</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>12.00 pcs</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>27.7992</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Setting Block Chair Use with E2-0177 Setting Block at Sill</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>E1-2530</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>46.33199999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Side Block For Intermediate Vertical Shallow Pocket</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>E2-0166</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>44.0154</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Setting Block For Sill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>E2-0177</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>44.0154</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1-1/8” “W” Side Block For Jamb</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>E2-0545</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>84.08399999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1/2” “W” Side Block For Intermediate Vertical Deep Pocket</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>E2-0154</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>32.4324</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Setting Block For Intermediate Horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>E2-0611</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18.00 pcs</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>54.483</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Total Accessory Cost</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>849.5000000000001</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>485.914</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>GASKETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Glazing Gasket For 1” Glazing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>720.00 ft</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>810</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E2-0052</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>720.00 ft</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>810</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>463.3199999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Total Gasket Cost</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>810</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>463.3199999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>DOORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Door (3' X 7')</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>10879.5</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6.00 pcs</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10879.5</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>10879.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Total Door Cost</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>10879.5</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>10879.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>GLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Glass Area (Adjusted)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>194.96 sqft</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2047.115</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>194.96 sqft</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>2047.115</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>2047.115</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Total Glass Cost</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>2047.115</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>2047.115</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Door Area (to subtract from glass)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>126.00 sqft</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>126.00 sqft</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Total Calculations Cost</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>FABRICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Part Number</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>72.00 joints</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>72.00 joints</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Total Fabrication Cost</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>COST/ELEVATION</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ELEVATION COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PROFILE COSTS</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>3354.923</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ACCESSORY COSTS</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>485.914</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>GASKET COSTS</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>463.3199999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DOOR COSTS</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>10879.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>GLASS COSTS</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>2047.115</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FABRICATION COSTS</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Elev 3 TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>18310.772</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>*Note - Elevation costs based on discounted material costs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -1729,37 +4956,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.00 ft</t>
+          <t>168.00 ft</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2 (24ft per)</t>
+          <t>7 (24ft per)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8ft x2, 3ft x4</t>
+          <t>8ft x12, 6ft x6, 3ft x12, 1ft x3</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>838</v>
+        <v>2933</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>514.532</v>
+        <v>1800.862</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18ft x1, 2ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.67%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J3" s="5" t="n">
-        <v>214.3883333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1775,24 +5002,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>120.00 ft</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>5 (24ft per)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8ft x3</t>
+          <t>8ft x15</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>92.09999999999999</v>
+        <v>460.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1821,24 +5048,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>120.00 ft</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>5 (24ft per)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8ft x3</t>
+          <t>8ft x15</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>497</v>
+        <v>2485</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>305.158</v>
+        <v>1525.79</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1867,37 +5094,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>72.00 ft</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>3 (24ft per)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3ft x4</t>
+          <t>6ft x6, 3ft x12, 1ft x3</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>527</v>
+        <v>1581</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>323.578</v>
+        <v>970.734</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>161.789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1913,37 +5140,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>72.00 ft</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>3 (24ft per)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3ft x4</t>
+          <t>6ft x6, 3ft x12, 1ft x3</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>444</v>
+        <v>1332</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>272.616</v>
+        <v>817.848</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>136.308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1959,37 +5186,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12.00 ft</t>
+          <t>72.00 ft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>3 (24ft per)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12ft</t>
+          <t>12ft x6</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>264</v>
+        <v>792</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>162.096</v>
+        <v>486.288</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12ft x1</t>
+          <t>0.00 ft</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>81.048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2005,37 +5232,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24.00 ft</t>
+          <t>180.00 ft</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1 (24ft per)</t>
+          <t>8 (24ft per)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3ft x8</t>
+          <t>6ft x18, 3ft x24, 1ft x9</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>85.05</v>
+        <v>680.4</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>52.2207</v>
+        <v>417.7656</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.00 ft</t>
+          <t>12ft x1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>26.11035</v>
       </c>
     </row>
     <row r="10">
@@ -2049,15 +5276,15 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2805.05</v>
+        <v>10553.4</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1722.3007</v>
+        <v>6479.787600000001</v>
       </c>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="9" t="n">
-        <v>593.5333333333333</v>
+        <v>26.11035</v>
       </c>
     </row>
     <row r="11">
@@ -2132,7 +5359,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.00 pcs</t>
+          <t>12.00 pcs</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2153,16 +5380,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>90.00%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>35.80848</v>
+        <v>15.91488</v>
       </c>
     </row>
     <row r="14">
@@ -2178,7 +5405,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>42.00 pcs</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2199,16 +5426,16 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>16.00%</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
-        <v>61.37544</v>
+        <v>11.69056</v>
       </c>
     </row>
     <row r="15">
@@ -2224,7 +5451,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.00 pcs</t>
+          <t>348.00 pcs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2234,27 +5461,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 order</t>
+          <t>4 orders</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
-        <v>18.3</v>
+        <v>73.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>11.2362</v>
+        <v>44.9448</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>52.00 pcs</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>44.00%</t>
+          <t>13.00%</t>
         </is>
       </c>
       <c r="J15" s="5" t="n">
-        <v>4.943928</v>
+        <v>5.842824</v>
       </c>
     </row>
     <row r="16">
@@ -2270,7 +5497,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.00 pcs</t>
+          <t>63.00 pcs</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2291,16 +5518,16 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>88.00 pcs</t>
+          <t>37.00 pcs</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>37.00%</t>
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>25.205928</v>
+        <v>10.597947</v>
       </c>
     </row>
     <row r="17">
@@ -2316,7 +5543,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>24.00 pcs</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2337,16 +5564,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>96.00 pcs</t>
+          <t>76.00 pcs</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>96.00%</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>28.646784</v>
+        <v>22.678704</v>
       </c>
     </row>
     <row r="18">
@@ -2362,7 +5589,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>42.00 pcs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2372,14 +5599,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8 orders</t>
+          <t>42 orders</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>22.104</v>
+        <v>116.046</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2408,7 +5635,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>36.00 pcs</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2429,16 +5656,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>14.00 pcs</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>28.00%</t>
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>41.57762400000001</v>
+        <v>13.229244</v>
       </c>
     </row>
     <row r="20">
@@ -2454,7 +5681,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>42.00 pcs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2475,16 +5702,16 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>16.00%</t>
         </is>
       </c>
       <c r="J20" s="5" t="n">
-        <v>39.687732</v>
+        <v>7.559568000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2500,7 +5727,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.00 pcs</t>
+          <t>30.00 pcs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2521,16 +5748,16 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46.00 pcs</t>
+          <t>20.00 pcs</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>92.00%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>83.03736000000001</v>
+        <v>36.1032</v>
       </c>
     </row>
     <row r="22">
@@ -2546,7 +5773,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.00 pcs</t>
+          <t>36.00 pcs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2567,16 +5794,16 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>44.00 pcs</t>
+          <t>14.00 pcs</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>88.00%</t>
+          <t>28.00%</t>
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>30.63614400000001</v>
+        <v>9.747864</v>
       </c>
     </row>
     <row r="23">
@@ -2592,7 +5819,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.00 pcs</t>
+          <t>42.00 pcs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2613,16 +5840,16 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42.00 pcs</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>16.00%</t>
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>49.12614</v>
+        <v>9.35736</v>
       </c>
     </row>
     <row r="24">
@@ -2636,15 +5863,15 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>786.2</v>
+        <v>994.1000000000001</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>482.7268</v>
+        <v>610.3774000000001</v>
       </c>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="9" t="n">
-        <v>400.04556</v>
+        <v>142.722151</v>
       </c>
     </row>
     <row r="25">
@@ -2719,37 +5946,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>224.00 ft</t>
+          <t>1392.00 ft</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1 (500ft per)</t>
+          <t>3 (500ft per)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>224ft</t>
+          <t>720ft x1, 448ft x1, 224ft x1</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>405</v>
+        <v>1215</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>248.67</v>
+        <v>746.01</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>276ft x1</t>
+          <t>276ft x1, 52ft x1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>55.20%</t>
+          <t>19.07%</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>137.26584</v>
+        <v>163.12752</v>
       </c>
     </row>
     <row r="28">
@@ -2763,21 +5990,21 @@
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>405</v>
+        <v>1215</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>248.67</v>
+        <v>746.01</v>
       </c>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="9" t="n">
-        <v>137.26584</v>
+        <v>163.12752</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>GLASS</t>
+          <t>DOORS</t>
         </is>
       </c>
     </row>
@@ -2836,12 +6063,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (3' X 7')</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Glass Area (Adjusted)</t>
+          <t>Door (3' X 7')</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2851,19 +6078,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>$10.50</t>
+          <t>$1769.44</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.75 sqft</t>
+          <t>8.00 pcs</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>879.375</v>
+        <v>14155.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>879.375</v>
+        <v>14155.5</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2886,14 +6113,14 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Total Glass Cost</t>
+          <t>Total Door Cost</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>879.375</v>
+        <v>14155.5</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>879.375</v>
+        <v>14155.5</v>
       </c>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
@@ -2904,7 +6131,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>LABOR</t>
+          <t>GLASS</t>
         </is>
       </c>
     </row>
@@ -2963,12 +6190,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Joints Fabrication Labor</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Joints Fabrication Labor</t>
+          <t>Glass Area (Adjusted)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2978,19 +6205,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>$15.00</t>
+          <t>$10.50</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.00 joints</t>
+          <t>434.66 sqft</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>360</v>
+        <v>4563.965</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>360</v>
+        <v>4563.965</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3013,14 +6240,14 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Total Labor Cost</t>
+          <t>Total Glass Cost</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>360</v>
+        <v>4563.965</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>360</v>
+        <v>4563.965</v>
       </c>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
@@ -3029,162 +6256,289 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>LABOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Project Total Materials</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Total Quantity Required</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Total List Cost</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Discounted Total List Cost</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Quantity</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Waste %</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Residual Material Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Joints Fabrication Labor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>$15.00</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>144.00 joints</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Total Labor Cost</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>COST OVERVIEW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>List Price Total:</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>5235.625</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="C42" s="18" t="n">
+        <v>33641.965</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Discounted Total:</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="C43" s="20" t="n">
+        <v>28715.64</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Residual/Waste Cost:</t>
         </is>
       </c>
-      <c r="C40" s="18" t="n">
-        <v>1130.844733333333</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="C44" s="18" t="n">
+        <v>331.960021</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Waste Percentage:</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>ADDITIONAL COSTS</t>
         </is>
       </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="26" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="26" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>(None configured)</t>
         </is>
       </c>
-      <c r="C43" s="28" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="C47" s="28" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n"/>
-      <c r="C44" s="31" t="n">
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>MARKUPS / PROFIT</t>
         </is>
       </c>
-      <c r="B45" s="33" t="n"/>
-      <c r="C45" s="34" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="27" t="inlineStr">
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="34" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>(None configured)</t>
         </is>
       </c>
-      <c r="C46" s="28" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="C50" s="28" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="B47" s="30" t="n"/>
-      <c r="C47" s="31" t="n">
+      <c r="B51" s="30" t="n"/>
+      <c r="C51" s="31" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>PROJECT TOTAL</t>
         </is>
       </c>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="37" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="B52" s="36" t="n"/>
+      <c r="C52" s="37" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="38" t="inlineStr">
         <is>
           <t>Discounted Total:</t>
         </is>
       </c>
-      <c r="B49" s="39" t="n"/>
-      <c r="C49" s="40" t="n">
-        <v>3693.0725</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="40" t="n">
+        <v>28715.64</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>+ Additional:</t>
         </is>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C54" s="18" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>+ Markups:</t>
         </is>
       </c>
-      <c r="C51" s="18" t="n">
+      <c r="C55" s="18" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="41" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
         <is>
           <t>GRAND TOTAL:</t>
         </is>
       </c>
-      <c r="B52" s="42" t="n"/>
-      <c r="C52" s="43" t="n">
-        <v>3693.0725</v>
+      <c r="B56" s="42" t="n"/>
+      <c r="C56" s="43" t="n">
+        <v>28715.64</v>
       </c>
     </row>
   </sheetData>
